--- a/Curs Oficial/sesiuni/s05/echipa_rosu/Produse.xlsx
+++ b/Curs Oficial/sesiuni/s05/echipa_rosu/Produse.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dim_Produse" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produse" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
         <v>42</v>
       </c>
       <c r="H4" t="n">
-        <v>10.53</v>
+        <v>0.35</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         <v>38</v>
       </c>
       <c r="H5" t="n">
-        <v>6.48</v>
+        <v>0.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         <v>28</v>
       </c>
       <c r="H6" t="n">
-        <v>7.49</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>3.85</v>
+        <v>0.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -688,7 +688,6 @@
           <t>Pizza Margherita</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Pizza</t>
@@ -705,7 +704,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>11.21</v>
+        <v>0.45</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -746,7 +745,7 @@
         <v>18</v>
       </c>
       <c r="H9" t="n">
-        <v>8.83</v>
+        <v>0.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -787,7 +786,7 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>9.48</v>
+        <v>0.05</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -809,7 +808,6 @@
           <t>Vin rosu pahar</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Alcool</t>
@@ -824,7 +822,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="n">
-        <v>2.99</v>
+        <v>0.15</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -846,7 +844,6 @@
           <t>Apa minerala 0.5L</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Non-alcool</t>
@@ -861,7 +858,7 @@
         <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>4.58</v>
+        <v>0.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -902,7 +899,7 @@
         <v>26</v>
       </c>
       <c r="H13" t="n">
-        <v>1.33</v>
+        <v>0.15</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -922,7 +919,6 @@
           <t>Papanasi</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Traditional</t>
@@ -937,7 +933,7 @@
         <v>29</v>
       </c>
       <c r="H14" t="n">
-        <v>4.35</v>
+        <v>0.25</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -978,7 +974,7 @@
         <v>32</v>
       </c>
       <c r="H15" t="n">
-        <v>1.62</v>
+        <v>0.35</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1019,7 +1015,7 @@
         <v>320</v>
       </c>
       <c r="H16" t="n">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1060,7 +1056,7 @@
         <v>450</v>
       </c>
       <c r="H17" t="n">
-        <v>11.19</v>
+        <v>4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1101,7 +1097,7 @@
         <v>36</v>
       </c>
       <c r="H18" t="n">
-        <v>5.14</v>
+        <v>0.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1142,7 +1138,7 @@
         <v>16</v>
       </c>
       <c r="H19" t="n">
-        <v>8.140000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1183,7 +1179,7 @@
         <v>15</v>
       </c>
       <c r="H20" t="n">
-        <v>8.19</v>
+        <v>0.15</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1224,7 +1220,7 @@
         <v>34</v>
       </c>
       <c r="H21" t="n">
-        <v>6.81</v>
+        <v>0.3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1238,14 +1234,6 @@
           <t>Categorii: fill-down manual daca lipseste</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
